--- a/data/WP17_auswertung_sachgebiete.xlsx
+++ b/data/WP17_auswertung_sachgebiete.xlsx
@@ -4154,13 +4154,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDD35F33-E225-4EF4-93E4-6C7019884D9F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D0F33B5-68BD-4E35-B014-2B0A95C8E77B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C846DD6D-1029-4875-93A6-834DA410F3C1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10002427-5DDC-4E8F-A4DF-7560EB3A5699}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB5730BC-0743-4CE3-A2A1-BD13A6C50B71}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6425E933-9B9A-4232-A224-B1C52A8B4F25}"/>
 </file>